--- a/samples/ma-dia-peril-13-template.xlsx
+++ b/samples/ma-dia-peril-13-template.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\code\excel-template-engine\samples\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C7A3830-35C5-4553-A3FE-A2148FDE5971}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32005EB2-DEA6-4973-A5C1-59007EC4473D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{DDCC0EFB-3F72-490E-8902-D1E0593C56B5}"/>
   </bookViews>
@@ -77,18 +77,9 @@
     <t>Assessment Reason</t>
   </si>
   <si>
-    <t>{{reportId}}</t>
-  </si>
-  <si>
     <t>{{title}}</t>
   </si>
   <si>
-    <t>{{runDate}}</t>
-  </si>
-  <si>
-    <t>{{period}}</t>
-  </si>
-  <si>
     <t>{{rows.companyCode}}</t>
   </si>
   <si>
@@ -123,6 +114,15 @@
   </si>
   <si>
     <t>{{rows.assessmentReason}}</t>
+  </si>
+  <si>
+    <t>{{runDateLine}}</t>
+  </si>
+  <si>
+    <t>{{periodLine}}</t>
+  </si>
+  <si>
+    <t>{{reportLabel}}</t>
   </si>
 </sst>
 </file>
@@ -550,22 +550,22 @@
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
     </row>
     <row r="6" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
@@ -608,40 +608,40 @@
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D7" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="E7" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="F7" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="G7" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="E7" s="2" t="s">
+      <c r="H7" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="F7" s="2" t="s">
+      <c r="I7" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="G7" s="3" t="s">
+      <c r="J7" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="H7" s="2" t="s">
+      <c r="K7" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="I7" s="5" t="s">
+      <c r="L7" s="2" t="s">
         <v>24</v>
-      </c>
-      <c r="J7" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="K7" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="L7" s="2" t="s">
-        <v>27</v>
       </c>
     </row>
   </sheetData>
